--- a/03_IE_tasks/data/related/outcomes_endpoints/Endpoints_burrowsAnimalModelsMultiple2019.xlsx
+++ b/03_IE_tasks/data/related/outcomes_endpoints/Endpoints_burrowsAnimalModelsMultiple2019.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sdoneva/Documents/Work/In Progress/PhD/PhD Projects/In Progress/Preclinical_Pipeline/03_IE_tasks/data/related/outcomes_endpoints/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D26887C3-79FA-744D-9097-34BCB1855ABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{674C0FF1-1610-E54B-BA7B-02130C0C194C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="1320" windowWidth="27640" windowHeight="16940" xr2:uid="{9ED72F13-1A67-B841-A737-FA12732D0988}"/>
+    <workbookView xWindow="46440" yWindow="3840" windowWidth="27640" windowHeight="16940" xr2:uid="{9ED72F13-1A67-B841-A737-FA12732D0988}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="38">
   <si>
     <t>Test Name</t>
   </si>
@@ -96,6 +96,60 @@
   </si>
   <si>
     <t>Rotarod</t>
+  </si>
+  <si>
+    <t>Tail paralysis</t>
+  </si>
+  <si>
+    <t>Presence of tail flaccidity/paralysis</t>
+  </si>
+  <si>
+    <t>Sensorimotor deficit</t>
+  </si>
+  <si>
+    <t>Hindlimb paresis</t>
+  </si>
+  <si>
+    <t>Loss of coordinated hindlimb movements</t>
+  </si>
+  <si>
+    <t>Bilateral hindlimb paralysis</t>
+  </si>
+  <si>
+    <t>Paralysis of both hindlimbs</t>
+  </si>
+  <si>
+    <t>Forelimb paralysis</t>
+  </si>
+  <si>
+    <t>Paralysis of forelimbs</t>
+  </si>
+  <si>
+    <t>Moribund status</t>
+  </si>
+  <si>
+    <t>Animal in moribund (near death) condition</t>
+  </si>
+  <si>
+    <t>Survival/Mortality</t>
+  </si>
+  <si>
+    <t>Clinical score evaluation</t>
+  </si>
+  <si>
+    <t>Composite neurological severity score (1–5)</t>
+  </si>
+  <si>
+    <t>Global well-being</t>
+  </si>
+  <si>
+    <t>Hindlimb paralysis</t>
+  </si>
+  <si>
+    <t>Paralysis of hindlimbs</t>
+  </si>
+  <si>
+    <t>Physiology</t>
   </si>
 </sst>
 </file>
@@ -476,10 +530,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{230C1DF2-EBA7-194A-9667-E971EF9B423D}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
@@ -566,6 +621,104 @@
         <v>17</v>
       </c>
     </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/03_IE_tasks/data/related/outcomes_endpoints/Endpoints_burrowsAnimalModelsMultiple2019.xlsx
+++ b/03_IE_tasks/data/related/outcomes_endpoints/Endpoints_burrowsAnimalModelsMultiple2019.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sdoneva/Documents/Work/In Progress/PhD/PhD Projects/In Progress/Preclinical_Pipeline/03_IE_tasks/data/related/outcomes_endpoints/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{674C0FF1-1610-E54B-BA7B-02130C0C194C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0930AFFB-B7D4-6540-B197-EE914778E03F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="46440" yWindow="3840" windowWidth="27640" windowHeight="16940" xr2:uid="{9ED72F13-1A67-B841-A737-FA12732D0988}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="42">
   <si>
     <t>Test Name</t>
   </si>
@@ -150,6 +150,18 @@
   </si>
   <si>
     <t>Physiology</t>
+  </si>
+  <si>
+    <t>Tail weakness</t>
+  </si>
+  <si>
+    <t>Degree of tail droop or inability to lift tail when lifted by the base</t>
+  </si>
+  <si>
+    <t>Forelimb paresis</t>
+  </si>
+  <si>
+    <t>Degree of weakness or inability to bear weight on one or both forelimbs during movement or when</t>
   </si>
 </sst>
 </file>
@@ -530,10 +542,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{230C1DF2-EBA7-194A-9667-E971EF9B423D}">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
+    <col min="2" max="2" width="67.6640625" customWidth="1"/>
     <col min="3" max="3" width="22.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -623,10 +636,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="C7" t="s">
         <v>5</v>
@@ -637,10 +650,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
         <v>5</v>
@@ -651,10 +664,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
@@ -665,10 +678,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
         <v>5</v>
@@ -679,43 +692,71 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
         <v>5</v>
       </c>
       <c r="D12" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
         <v>35</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B15" t="s">
         <v>36</v>
       </c>
-      <c r="C13" t="s">
-        <v>5</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="C15" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15" t="s">
         <v>22</v>
       </c>
     </row>
